--- a/tenant_application_forms/025_online_rental_application_form--tenant_application_forms.xlsx
+++ b/tenant_application_forms/025_online_rental_application_form--tenant_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Preferred Method Of Rental Payment Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rental Status Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Income Frequency Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
